--- a/03_Outputs/Agua_Bosques_Turismo/10_Seguridad/seguridad.xlsx
+++ b/03_Outputs/Agua_Bosques_Turismo/10_Seguridad/seguridad.xlsx
@@ -19,20 +19,23 @@
     <sheet name="P6_cambio_municipio" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="irv" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="desaparecidos" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="_fig_01" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="_fig_02" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="_fig_03" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="_fig_04" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="_fig_05" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="_mapa10_homicidios" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="_mapa10_homicidios_dpto" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="reparacion_colectiva" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="reparacion_colectiva_sujetos" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="_fig_01" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="_fig_02" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="_fig_03" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="_fig_04" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="_fig_05" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="_fig_06" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="_mapa10_homicidios" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="_mapa10_homicidios_dpto" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="68">
+  <numFmts count="75">
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
@@ -101,8 +104,15 @@
     <numFmt numFmtId="230" formatCode="#,##0"/>
     <numFmt numFmtId="231" formatCode="0.0%"/>
     <numFmt numFmtId="232" formatCode="0.0%"/>
+    <numFmt numFmtId="233" formatCode="#,##0"/>
+    <numFmt numFmtId="234" formatCode="#,##0"/>
+    <numFmt numFmtId="235" formatCode="#,##0"/>
+    <numFmt numFmtId="236" formatCode="#,##0"/>
+    <numFmt numFmtId="237" formatCode="0.0%"/>
+    <numFmt numFmtId="238" formatCode="0.0%"/>
+    <numFmt numFmtId="239" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,23 +122,307 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -148,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -159,68 +453,126 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="171" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="173" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="174" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="175" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="171" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="173" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="175" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="176" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="177" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="177" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="178" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="179" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="179" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="180" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="181" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="181" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="182" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="183" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="183" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="184" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="185" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="185" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="186" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="187" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="187" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="188" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="189" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="189" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="190" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="191" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="191" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="192" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="193" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="193" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="196" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="197" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="197" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="198" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="199" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="199" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="200" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="201" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="201" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="202" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="203" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="13" numFmtId="203" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="204" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="205" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="13" numFmtId="205" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="206" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="207" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="13" numFmtId="207" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="14" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="15" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="214" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="16" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="17" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="18" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="14" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="20" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="20" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="15" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="22" numFmtId="234" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="22" numFmtId="236" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="22" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="16" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="17" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="18" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="19" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="20" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="21" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="22" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="23" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="24" fontId="31" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,13 +901,13 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -725,46 +1077,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="5" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="79" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="79" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="79" t="inlineStr">
         <is>
           <t>Muy seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="79" t="inlineStr">
         <is>
           <t>Seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="79" t="inlineStr">
         <is>
           <t>Inseguro (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="79" t="inlineStr">
         <is>
           <t>Muy inseguro (%)</t>
         </is>
@@ -781,19 +1134,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="61">
+      <c r="C2" s="84">
         <v>424</v>
       </c>
-      <c r="D2" s="57">
+      <c r="D2" s="80">
         <v>0.0495308294015769</v>
       </c>
-      <c r="E2" s="58">
+      <c r="E2" s="81">
         <v>0.729867318937959</v>
       </c>
-      <c r="F2" s="59">
+      <c r="F2" s="82">
         <v>0.201754631420135</v>
       </c>
-      <c r="G2" s="60">
+      <c r="G2" s="83">
         <v>0.0188472202403288</v>
       </c>
     </row>
@@ -808,19 +1161,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="61">
+      <c r="C3" s="84">
         <v>424</v>
       </c>
-      <c r="D3" s="57">
+      <c r="D3" s="80">
         <v>0.130277574381468</v>
       </c>
-      <c r="E3" s="58">
+      <c r="E3" s="81">
         <v>0.656307439137242</v>
       </c>
-      <c r="F3" s="59">
+      <c r="F3" s="82">
         <v>0.172963294129803</v>
       </c>
-      <c r="G3" s="60">
+      <c r="G3" s="83">
         <v>0.0404516923514872</v>
       </c>
     </row>
@@ -835,19 +1188,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="61">
+      <c r="C4" s="84">
         <v>424</v>
       </c>
-      <c r="D4" s="57">
+      <c r="D4" s="80">
         <v>0.0781778388488264</v>
       </c>
-      <c r="E4" s="58">
+      <c r="E4" s="81">
         <v>0.718261818032703</v>
       </c>
-      <c r="F4" s="59">
+      <c r="F4" s="82">
         <v>0.173614335003494</v>
       </c>
-      <c r="G4" s="60">
+      <c r="G4" s="83">
         <v>0.0299460081149764</v>
       </c>
     </row>
@@ -862,19 +1215,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="61">
+      <c r="C5" s="84">
         <v>424</v>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="80">
         <v>0.0802303393725371</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="81">
         <v>0.682605191125798</v>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="82">
         <v>0.203255514273681</v>
       </c>
-      <c r="G5" s="60">
+      <c r="G5" s="83">
         <v>0.0339089552279842</v>
       </c>
     </row>
@@ -889,19 +1242,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="61">
+      <c r="C6" s="84">
         <v>416</v>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="80">
         <v>0.103857561799856</v>
       </c>
-      <c r="E6" s="58">
+      <c r="E6" s="81">
         <v>0.587729631702723</v>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="82">
         <v>0.286862397760999</v>
       </c>
-      <c r="G6" s="60">
+      <c r="G6" s="83">
         <v>0.0215504087364212</v>
       </c>
     </row>
@@ -916,19 +1269,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="61">
+      <c r="C7" s="84">
         <v>920</v>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="80">
         <v>0.0768822965634978</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="81">
         <v>0.594177699261182</v>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="82">
         <v>0.275475383235366</v>
       </c>
-      <c r="G7" s="60">
+      <c r="G7" s="83">
         <v>0.0534646209399541</v>
       </c>
     </row>
@@ -943,19 +1296,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="61">
+      <c r="C8" s="84">
         <v>352</v>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="80">
         <v>0.0687742553944103</v>
       </c>
-      <c r="E8" s="58">
+      <c r="E8" s="81">
         <v>0.625178085085976</v>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="82">
         <v>0.247095646865967</v>
       </c>
-      <c r="G8" s="60">
+      <c r="G8" s="83">
         <v>0.0589520126536461</v>
       </c>
     </row>
@@ -970,19 +1323,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="61">
+      <c r="C9" s="84">
         <v>365</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="80">
         <v>0.0895956895119396</v>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="81">
         <v>0.681839471598318</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="82">
         <v>0.189919810636675</v>
       </c>
-      <c r="G9" s="60">
+      <c r="G9" s="83">
         <v>0.0386450282530676</v>
       </c>
     </row>
@@ -998,47 +1351,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="86" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="86" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="86" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="86" t="inlineStr">
         <is>
           <t>Más seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="86" t="inlineStr">
         <is>
           <t>Menos seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="86" t="inlineStr">
         <is>
           <t>Igual (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="86" t="inlineStr">
         <is>
           <t>No sabe/No responde (%)</t>
         </is>
@@ -1055,19 +1408,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="66">
+      <c r="C2" s="91">
         <v>424</v>
       </c>
-      <c r="D2" s="62">
+      <c r="D2" s="87">
         <v>0.138381661852711</v>
       </c>
-      <c r="E2" s="63">
+      <c r="E2" s="88">
         <v>0.0947782683838063</v>
       </c>
-      <c r="F2" s="64">
+      <c r="F2" s="89">
         <v>0.745345158365962</v>
       </c>
-      <c r="G2" s="65">
+      <c r="G2" s="90">
         <v>0.0214949113975205</v>
       </c>
     </row>
@@ -1082,19 +1435,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="66">
+      <c r="C3" s="91">
         <v>424</v>
       </c>
-      <c r="D3" s="62">
+      <c r="D3" s="87">
         <v>0.358267778822599</v>
       </c>
-      <c r="E3" s="63">
+      <c r="E3" s="88">
         <v>0.186607279276067</v>
       </c>
-      <c r="F3" s="64">
+      <c r="F3" s="89">
         <v>0.437728801051002</v>
       </c>
-      <c r="G3" s="65">
+      <c r="G3" s="90">
         <v>0.0173961408503314</v>
       </c>
     </row>
@@ -1109,19 +1462,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="66">
+      <c r="C4" s="91">
         <v>424</v>
       </c>
-      <c r="D4" s="62">
+      <c r="D4" s="87">
         <v>0.219114065875647</v>
       </c>
-      <c r="E4" s="63">
+      <c r="E4" s="88">
         <v>0.166237698869039</v>
       </c>
-      <c r="F4" s="64">
+      <c r="F4" s="89">
         <v>0.61279770674214</v>
       </c>
-      <c r="G4" s="65">
+      <c r="G4" s="90">
         <v>0.00185052851317393</v>
       </c>
     </row>
@@ -1136,19 +1489,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="66">
+      <c r="C5" s="91">
         <v>424</v>
       </c>
-      <c r="D5" s="62">
+      <c r="D5" s="87">
         <v>0.170668487949013</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="88">
         <v>0.21205173765484</v>
       </c>
-      <c r="F5" s="64">
+      <c r="F5" s="89">
         <v>0.607107231470942</v>
       </c>
-      <c r="G5" s="65">
+      <c r="G5" s="90">
         <v>0.0101725429252042</v>
       </c>
     </row>
@@ -1163,19 +1516,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="66">
+      <c r="C6" s="91">
         <v>416</v>
       </c>
-      <c r="D6" s="62">
+      <c r="D6" s="87">
         <v>0.159215120550686</v>
       </c>
-      <c r="E6" s="63">
+      <c r="E6" s="88">
         <v>0.170584025983668</v>
       </c>
-      <c r="F6" s="64">
+      <c r="F6" s="89">
         <v>0.66470460425813</v>
       </c>
-      <c r="G6" s="65">
+      <c r="G6" s="90">
         <v>0.00549624920751532</v>
       </c>
     </row>
@@ -1190,19 +1543,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="66">
+      <c r="C7" s="91">
         <v>920</v>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="87">
         <v>0.124866275152401</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="88">
         <v>0.214783934966638</v>
       </c>
-      <c r="F7" s="64">
+      <c r="F7" s="89">
         <v>0.648273839741865</v>
       </c>
-      <c r="G7" s="65">
+      <c r="G7" s="90">
         <v>0.0120759501390955</v>
       </c>
     </row>
@@ -1217,19 +1570,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="66">
+      <c r="C8" s="91">
         <v>352</v>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="87">
         <v>0.13996256285107</v>
       </c>
-      <c r="E8" s="63">
+      <c r="E8" s="88">
         <v>0.17884149937376</v>
       </c>
-      <c r="F8" s="64">
+      <c r="F8" s="89">
         <v>0.668406683552147</v>
       </c>
-      <c r="G8" s="65">
+      <c r="G8" s="90">
         <v>0.0127892542230232</v>
       </c>
     </row>
@@ -1244,19 +1597,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="66">
+      <c r="C9" s="91">
         <v>365</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="87">
         <v>0.156798743025141</v>
       </c>
-      <c r="E9" s="63">
+      <c r="E9" s="88">
         <v>0.130998394519631</v>
       </c>
-      <c r="F9" s="64">
+      <c r="F9" s="89">
         <v>0.710067193397917</v>
       </c>
-      <c r="G9" s="65">
+      <c r="G9" s="90">
         <v>0.00213566905731085</v>
       </c>
     </row>
@@ -1272,41 +1625,41 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="93" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="93" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="93" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="93" t="inlineStr">
         <is>
           <t>Índice de Riesgo de Victimización</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="93" t="inlineStr">
         <is>
           <t>Categoría de riesgo</t>
         </is>
@@ -1331,7 +1684,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="67">
+      <c r="E2" s="94">
         <v>0.11001804</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -1359,7 +1712,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="67">
+      <c r="E3" s="94">
         <v>0.24209525</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -1387,7 +1740,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="67">
+      <c r="E4" s="94">
         <v>0.21846661</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -1415,7 +1768,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="67">
+      <c r="E5" s="94">
         <v>0.37289315</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -1443,7 +1796,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="67">
+      <c r="E6" s="94">
         <v>0.14975308</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -1471,7 +1824,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="67">
+      <c r="E7" s="94">
         <v>0.1249114</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -1499,7 +1852,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="67">
+      <c r="E8" s="94">
         <v>0.14330333</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -1527,7 +1880,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="67">
+      <c r="E9" s="94">
         <v>0.36460277</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -1555,7 +1908,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="67">
+      <c r="E10" s="94">
         <v>0.41134752</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -1583,7 +1936,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="67">
+      <c r="E11" s="94">
         <v>0.3524257</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -1611,7 +1964,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="67">
+      <c r="E12" s="94">
         <v>0.24324094</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -1639,7 +1992,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="67">
+      <c r="E13" s="94">
         <v>0.10889442</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -1660,41 +2013,41 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="96" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="96" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="96" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="96" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="96" t="inlineStr">
         <is>
           <t>Personas dadas por desaparecidas</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="96" t="inlineStr">
         <is>
           <t>Proporción dentro de la provincia</t>
         </is>
@@ -1719,10 +2072,10 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="68">
+      <c r="E2" s="98">
         <v>379</v>
       </c>
-      <c r="F2" s="70">
+      <c r="F2" s="100">
         <v>0.22969696969697</v>
       </c>
     </row>
@@ -1745,10 +2098,10 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="68">
+      <c r="E3" s="98">
         <v>263</v>
       </c>
-      <c r="F3" s="70">
+      <c r="F3" s="100">
         <v>0.159393939393939</v>
       </c>
     </row>
@@ -1771,10 +2124,10 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="68">
+      <c r="E4" s="98">
         <v>262</v>
       </c>
-      <c r="F4" s="70">
+      <c r="F4" s="100">
         <v>0.158787878787879</v>
       </c>
     </row>
@@ -1797,10 +2150,10 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="68">
+      <c r="E5" s="98">
         <v>188</v>
       </c>
-      <c r="F5" s="70">
+      <c r="F5" s="100">
         <v>0.113939393939394</v>
       </c>
     </row>
@@ -1823,10 +2176,10 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="68">
+      <c r="E6" s="98">
         <v>185</v>
       </c>
-      <c r="F6" s="70">
+      <c r="F6" s="100">
         <v>0.112121212121212</v>
       </c>
     </row>
@@ -1849,10 +2202,10 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="68">
+      <c r="E7" s="98">
         <v>171</v>
       </c>
-      <c r="F7" s="70">
+      <c r="F7" s="100">
         <v>0.103636363636364</v>
       </c>
     </row>
@@ -1875,10 +2228,10 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="68">
+      <c r="E8" s="98">
         <v>52</v>
       </c>
-      <c r="F8" s="70">
+      <c r="F8" s="100">
         <v>0.0315151515151515</v>
       </c>
     </row>
@@ -1901,10 +2254,10 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="68">
+      <c r="E9" s="98">
         <v>42</v>
       </c>
-      <c r="F9" s="70">
+      <c r="F9" s="100">
         <v>0.0254545454545455</v>
       </c>
     </row>
@@ -1927,10 +2280,10 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="68">
+      <c r="E10" s="98">
         <v>37</v>
       </c>
-      <c r="F10" s="70">
+      <c r="F10" s="100">
         <v>0.0224242424242424</v>
       </c>
     </row>
@@ -1953,10 +2306,10 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="68">
+      <c r="E11" s="98">
         <v>34</v>
       </c>
-      <c r="F11" s="70">
+      <c r="F11" s="100">
         <v>0.0206060606060606</v>
       </c>
     </row>
@@ -1979,10 +2332,10 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="68">
+      <c r="E12" s="98">
         <v>25</v>
       </c>
-      <c r="F12" s="70">
+      <c r="F12" s="100">
         <v>0.0151515151515152</v>
       </c>
     </row>
@@ -2005,38 +2358,38 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="68">
+      <c r="E13" s="98">
         <v>12</v>
       </c>
-      <c r="F13" s="70">
+      <c r="F13" s="100">
         <v>0.00727272727272727</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="97" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="97" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="97" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="97" t="inlineStr">
         <is>
           <t>POVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E14" s="69">
+      <c r="E14" s="99">
         <v>1650</v>
       </c>
-      <c r="F14" s="71">
+      <c r="F14" s="101">
         <v>1</v>
       </c>
     </row>
@@ -2049,299 +2402,440 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="63.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="62.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>periodo</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>ambito</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>n_resp</t>
+      <c r="A1" s="103" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="103" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="103" t="inlineStr">
+        <is>
+          <t>Subregión</t>
+        </is>
+      </c>
+      <c r="D1" s="103" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="E1" s="103" t="inlineStr">
+        <is>
+          <t>Sujetos de reparación colectiva reconocidos</t>
+        </is>
+      </c>
+      <c r="F1" s="103" t="inlineStr">
+        <is>
+          <t>Sujetos con Plan Integral de Reparación Colectiva implementado</t>
+        </is>
+      </c>
+      <c r="G1" s="103" t="inlineStr">
+        <is>
+          <t>% de avance del PIRC, promedio (solo sujetos con plan activo)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>2018</v>
+        <v>5667</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>0.126861776739346</v>
-      </c>
-      <c r="D2">
-        <v>424</v>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E2" s="105">
+        <v>2</v>
+      </c>
+      <c r="F2" s="107">
+        <v>0</v>
+      </c>
+      <c r="G2" s="109">
+        <v>0.85714285714</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2019 (1)</t>
-        </is>
+      <c r="A3">
+        <v>5021</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>0.135273634312383</v>
-      </c>
-      <c r="D3">
-        <v>424</v>
+          <t>Alejandría</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E3" s="105">
+        <v>1</v>
+      </c>
+      <c r="F3" s="107">
+        <v>0</v>
+      </c>
+      <c r="G3" s="109">
+        <v>0.044444444444</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2019 (2)</t>
-        </is>
+      <c r="A4">
+        <v>5197</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>0.14788090533506</v>
-      </c>
-      <c r="D4">
-        <v>424</v>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E4" s="105">
+        <v>1</v>
+      </c>
+      <c r="F4" s="107">
+        <v>1</v>
+      </c>
+      <c r="G4" s="109">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>2021</v>
+        <v>5313</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>0.174702571701756</v>
-      </c>
-      <c r="D5">
-        <v>424</v>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E5" s="105">
+        <v>1</v>
+      </c>
+      <c r="F5" s="107">
+        <v>0</v>
+      </c>
+      <c r="G5" s="109">
+        <v>0.875</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>2022</v>
+        <v>5440</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>0.157798401926723</v>
-      </c>
-      <c r="D6">
-        <v>416</v>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E6" s="105">
+        <v>1</v>
+      </c>
+      <c r="F6" s="107">
+        <v>0</v>
+      </c>
+      <c r="G6" s="109">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>2023</v>
+        <v>5649</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0.254343252439605</v>
-      </c>
-      <c r="D7">
-        <v>920</v>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E7" s="105">
+        <v>1</v>
+      </c>
+      <c r="F7" s="107">
+        <v>0</v>
+      </c>
+      <c r="G7" s="109">
+        <v>0.74018518519</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>2024</v>
+        <v>5652</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>0.171203003688759</v>
-      </c>
-      <c r="D8">
-        <v>352</v>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E8" s="105">
+        <v>1</v>
+      </c>
+      <c r="F8" s="107">
+        <v>0</v>
+      </c>
+      <c r="G8" s="109">
+        <v>0.84126984127</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>2025</v>
+        <v>5660</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.166059316349513</v>
-      </c>
-      <c r="D9">
-        <v>365</v>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E9" s="105">
+        <v>1</v>
+      </c>
+      <c r="F9" s="107">
+        <v>0</v>
+      </c>
+      <c r="G9" s="109">
+        <v>0.74166666667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>2018</v>
+        <v>5206</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>0.220601851660464</v>
-      </c>
-      <c r="D10">
-        <v>424</v>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E10" s="105">
+        <v>0</v>
+      </c>
+      <c r="F10" s="107">
+        <v>0</v>
+      </c>
+      <c r="G10" s="109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2019 (1)</t>
-        </is>
+      <c r="A11">
+        <v>5321</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>0.21341498648129</v>
-      </c>
-      <c r="D11">
-        <v>424</v>
+          <t>Guatapé</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E11" s="105">
+        <v>0</v>
+      </c>
+      <c r="F11" s="107">
+        <v>0</v>
+      </c>
+      <c r="G11" s="109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2019 (2)</t>
-        </is>
+      <c r="A12">
+        <v>5541</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>0.203560343118471</v>
-      </c>
-      <c r="D12">
-        <v>424</v>
+          <t>Peñol</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E12" s="105">
+        <v>0</v>
+      </c>
+      <c r="F12" s="107">
+        <v>0</v>
+      </c>
+      <c r="G12" s="109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>2021</v>
+        <v>5674</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>0.237164469501665</v>
-      </c>
-      <c r="D13">
-        <v>424</v>
+          <t>San Vicente Ferrer</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E13" s="105">
+        <v>0</v>
+      </c>
+      <c r="F13" s="107">
+        <v>0</v>
+      </c>
+      <c r="G13" s="109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>0.308412806497421</v>
-      </c>
-      <c r="D14">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>2023</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>0.32894000417532</v>
-      </c>
-      <c r="D15">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>2024</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>0.306047659519614</v>
-      </c>
-      <c r="D16">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>2025</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>0.228564838889742</v>
-      </c>
-      <c r="D17">
-        <v>365</v>
+      <c r="A14" s="104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="104" t="inlineStr">
+        <is>
+          <t>TOTAL PROVINCIA AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="C14" s="104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" s="104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="106">
+        <v>9</v>
+      </c>
+      <c r="F14" s="108">
+        <v>1</v>
+      </c>
+      <c r="G14" s="110">
+        <v>0.63746362433925</v>
       </c>
     </row>
   </sheetData>
@@ -2353,227 +2847,505 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="183.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>n_solicitudes</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>pob</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>tasa_solicitudes</t>
+      <c r="A1" s="112" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="112" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="112" t="inlineStr">
+        <is>
+          <t>Subregión</t>
+        </is>
+      </c>
+      <c r="D1" s="112" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="E1" s="112" t="inlineStr">
+        <is>
+          <t>Sujeto de reparación colectiva</t>
+        </is>
+      </c>
+      <c r="F1" s="112" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="G1" s="112" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="H1" s="112" t="inlineStr">
+        <is>
+          <t>Fase del Plan Integral de Reparación Colectiva</t>
+        </is>
+      </c>
+      <c r="I1" s="112" t="inlineStr">
+        <is>
+          <t>% de avance del PIRC</t>
+        </is>
+      </c>
+      <c r="J1" s="112" t="inlineStr">
+        <is>
+          <t>Zona PDET</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2">
+        <v>5021</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alejandría</t>
         </is>
       </c>
-      <c r="B2">
-        <v>47</v>
-      </c>
-      <c r="C2">
-        <v>5285</v>
-      </c>
-      <c r="D2">
-        <v>8.89309366130558</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>VEREDA LA INMACULADA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="I2" s="113">
+        <v>0.044444444444</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3">
+        <v>5197</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Cocorná</t>
         </is>
       </c>
-      <c r="B3">
-        <v>352</v>
-      </c>
-      <c r="C3">
-        <v>16089</v>
-      </c>
-      <c r="D3">
-        <v>21.8783019454286</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CABECERA MUNICIPAL DE COCORNA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="I3" s="113">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>37</v>
-      </c>
-      <c r="C4">
-        <v>5112</v>
-      </c>
-      <c r="D4">
-        <v>7.23787167449139</v>
+      <c r="A4">
+        <v>5313</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FOCALIZADO MUNICIPIO DE GRANADA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="I4" s="113">
+        <v>0.875</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>1390</v>
-      </c>
-      <c r="C5">
-        <v>10511</v>
-      </c>
-      <c r="D5">
-        <v>132.242412710494</v>
+      <c r="A5">
+        <v>5440</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO CÍVICO "RAMON EMILIO ARCILA" DEL ORIENTE ANTIOQUEÑO VÍCTIMA DEL CONFLICTO ARMADO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Organizaciones y Grupos</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>GRUPO</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="I5" s="113">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Guatapé</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>23</v>
-      </c>
-      <c r="C6">
-        <v>9695</v>
-      </c>
-      <c r="D6">
-        <v>2.37235688499226</v>
+      <c r="A6">
+        <v>5649</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FOCALIZADO MUNICIPIO DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="I6" s="113">
+        <v>0.74018518519</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Marinilla</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>74390</v>
-      </c>
-      <c r="D7">
-        <v>0.161312004301653</v>
+      <c r="A7">
+        <v>5652</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FOCALIZADO MUNICIPIO DE SAN FRANCISCO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="I7" s="113">
+        <v>0.84126984127</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Peñol</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>39</v>
-      </c>
-      <c r="C8">
-        <v>23827</v>
-      </c>
-      <c r="D8">
-        <v>1.63679858983506</v>
+      <c r="A8">
+        <v>5660</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CENTRO POBLADO BUENOS AIRES, VEREDAS LA ESTRELLA, VILLA NUEVA, LA MERCED, EL PORVENIR, MANIZALES, SAN FRANCISCO, EL SOCORRO, SOPETRÁN, LA AURORA, SAN ANTONIO, LOS PLANES Y SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="I8" s="113">
+        <v>0.74166666667</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>San Carlos</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2112</v>
-      </c>
-      <c r="C9">
-        <v>16938</v>
-      </c>
-      <c r="D9">
-        <v>124.690046050301</v>
+      <c r="A9">
+        <v>5667</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GRUPO LGBTI SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Organizaciones y Grupos</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>GRUPO OSIGD-LGBTI</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="I9" s="113" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>257</v>
-      </c>
-      <c r="C10">
-        <v>6058</v>
-      </c>
-      <c r="D10">
-        <v>42.4232419940574</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San Luis</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>437</v>
-      </c>
-      <c r="C11">
-        <v>14447</v>
-      </c>
-      <c r="D11">
-        <v>30.2484944971274</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A10">
+        <v>5667</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>San Rafael</t>
         </is>
       </c>
-      <c r="B12">
-        <v>403</v>
-      </c>
-      <c r="C12">
-        <v>17411</v>
-      </c>
-      <c r="D12">
-        <v>23.1462868301648</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>San Vicente Ferrer</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>32</v>
-      </c>
-      <c r="C13">
-        <v>24776</v>
-      </c>
-      <c r="D13">
-        <v>1.29157248950597</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>COMUNIDAD DEL ÁREA URBANA DEL MUNICIPIO DE SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="I10" s="113">
+        <v>0.85714285714</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2585,185 +3357,299 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>desaparecidos</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>prop_desaparecidos</t>
+      <c r="A1" s="115" t="inlineStr">
+        <is>
+          <t>periodo</t>
+        </is>
+      </c>
+      <c r="B1" s="115" t="inlineStr">
+        <is>
+          <t>ambito</t>
+        </is>
+      </c>
+      <c r="C1" s="115" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="D1" s="115" t="inlineStr">
+        <is>
+          <t>n_resp</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>San Carlos</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>379</v>
+      <c r="A2">
+        <v>2018</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C2">
-        <v>0.22969696969697</v>
+        <v>0.126861776739346</v>
+      </c>
+      <c r="D2">
+        <v>424</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>San Luis</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>263</v>
+          <t>2019 (1)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C3">
-        <v>0.159393939393939</v>
+        <v>0.135273634312383</v>
+      </c>
+      <c r="D3">
+        <v>424</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>262</v>
+          <t>2019 (2)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C4">
-        <v>0.158787878787879</v>
+        <v>0.14788090533506</v>
+      </c>
+      <c r="D4">
+        <v>424</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cocorná</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>188</v>
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C5">
-        <v>0.113939393939394</v>
+        <v>0.174702571701756</v>
+      </c>
+      <c r="D5">
+        <v>424</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>185</v>
+      <c r="A6">
+        <v>2022</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C6">
-        <v>0.112121212121212</v>
+        <v>0.157798401926723</v>
+      </c>
+      <c r="D6">
+        <v>416</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>San Rafael</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>171</v>
+      <c r="A7">
+        <v>2023</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C7">
-        <v>0.103636363636364</v>
+        <v>0.254343252439605</v>
+      </c>
+      <c r="D7">
+        <v>920</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Marinilla</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>52</v>
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C8">
-        <v>0.0315151515151515</v>
+        <v>0.171203003688759</v>
+      </c>
+      <c r="D8">
+        <v>352</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Alejandría</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>42</v>
+      <c r="A9">
+        <v>2025</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C9">
-        <v>0.0254545454545455</v>
+        <v>0.166059316349513</v>
+      </c>
+      <c r="D9">
+        <v>365</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Vicente Ferrer</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>37</v>
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
       </c>
       <c r="C10">
-        <v>0.0224242424242424</v>
+        <v>0.220601851660464</v>
+      </c>
+      <c r="D10">
+        <v>424</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>34</v>
+          <t>2019 (1)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
       </c>
       <c r="C11">
-        <v>0.0206060606060606</v>
+        <v>0.21341498648129</v>
+      </c>
+      <c r="D11">
+        <v>424</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Peñol</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>25</v>
+          <t>2019 (2)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
       </c>
       <c r="C12">
-        <v>0.0151515151515152</v>
+        <v>0.203560343118471</v>
+      </c>
+      <c r="D12">
+        <v>424</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Guatapé</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>12</v>
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
       </c>
       <c r="C13">
-        <v>0.00727272727272727</v>
+        <v>0.237164469501665</v>
+      </c>
+      <c r="D13">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0.308412806497421</v>
+      </c>
+      <c r="D14">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>0.32894000417532</v>
+      </c>
+      <c r="D15">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0.306047659519614</v>
+      </c>
+      <c r="D16">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0.228564838889742</v>
+      </c>
+      <c r="D17">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -2775,22 +3661,34 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="117" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>victimas_ocurrencia</t>
+      <c r="B1" s="117" t="inlineStr">
+        <is>
+          <t>n_solicitudes</t>
+        </is>
+      </c>
+      <c r="C1" s="117" t="inlineStr">
+        <is>
+          <t>pob</t>
+        </is>
+      </c>
+      <c r="D1" s="117" t="inlineStr">
+        <is>
+          <t>tasa_solicitudes</t>
         </is>
       </c>
     </row>
@@ -2801,7 +3699,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>7678</v>
+        <v>47</v>
+      </c>
+      <c r="C2">
+        <v>5285</v>
+      </c>
+      <c r="D2">
+        <v>8.89309366130558</v>
       </c>
     </row>
     <row r="3">
@@ -2811,7 +3715,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>39522</v>
+        <v>352</v>
+      </c>
+      <c r="C3">
+        <v>16089</v>
+      </c>
+      <c r="D3">
+        <v>21.8783019454286</v>
       </c>
     </row>
     <row r="4">
@@ -2821,7 +3731,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>4469</v>
+        <v>37</v>
+      </c>
+      <c r="C4">
+        <v>5112</v>
+      </c>
+      <c r="D4">
+        <v>7.23787167449139</v>
       </c>
     </row>
     <row r="5">
@@ -2831,7 +3747,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>42239</v>
+        <v>1390</v>
+      </c>
+      <c r="C5">
+        <v>10511</v>
+      </c>
+      <c r="D5">
+        <v>132.242412710494</v>
       </c>
     </row>
     <row r="6">
@@ -2841,7 +3763,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>2915</v>
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>9695</v>
+      </c>
+      <c r="D6">
+        <v>2.37235688499226</v>
       </c>
     </row>
     <row r="7">
@@ -2851,7 +3779,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>7118</v>
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>74390</v>
+      </c>
+      <c r="D7">
+        <v>0.161312004301653</v>
       </c>
     </row>
     <row r="8">
@@ -2861,7 +3795,13 @@
         </is>
       </c>
       <c r="B8">
-        <v>7851</v>
+        <v>39</v>
+      </c>
+      <c r="C8">
+        <v>23827</v>
+      </c>
+      <c r="D8">
+        <v>1.63679858983506</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +3811,13 @@
         </is>
       </c>
       <c r="B9">
-        <v>46959</v>
+        <v>2112</v>
+      </c>
+      <c r="C9">
+        <v>16938</v>
+      </c>
+      <c r="D9">
+        <v>124.690046050301</v>
       </c>
     </row>
     <row r="10">
@@ -2881,7 +3827,13 @@
         </is>
       </c>
       <c r="B10">
-        <v>21242</v>
+        <v>257</v>
+      </c>
+      <c r="C10">
+        <v>6058</v>
+      </c>
+      <c r="D10">
+        <v>42.4232419940574</v>
       </c>
     </row>
     <row r="11">
@@ -2891,7 +3843,13 @@
         </is>
       </c>
       <c r="B11">
-        <v>36685</v>
+        <v>437</v>
+      </c>
+      <c r="C11">
+        <v>14447</v>
+      </c>
+      <c r="D11">
+        <v>30.2484944971274</v>
       </c>
     </row>
     <row r="12">
@@ -2901,7 +3859,13 @@
         </is>
       </c>
       <c r="B12">
-        <v>28701</v>
+        <v>403</v>
+      </c>
+      <c r="C12">
+        <v>17411</v>
+      </c>
+      <c r="D12">
+        <v>23.1462868301648</v>
       </c>
     </row>
     <row r="13">
@@ -2911,7 +3875,13 @@
         </is>
       </c>
       <c r="B13">
-        <v>11614</v>
+        <v>32</v>
+      </c>
+      <c r="C13">
+        <v>24776</v>
+      </c>
+      <c r="D13">
+        <v>1.29157248950597</v>
       </c>
     </row>
   </sheetData>
@@ -2923,237 +3893,185 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>hecho</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>victimas_ocurrencia</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>proporcion_pct</t>
+      <c r="A1" s="119" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="119" t="inlineStr">
+        <is>
+          <t>desaparecidos</t>
+        </is>
+      </c>
+      <c r="C1" s="119" t="inlineStr">
+        <is>
+          <t>prop_desaparecidos</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Desplazamiento forzado</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="B2">
-        <v>212721</v>
+        <v>379</v>
       </c>
       <c r="C2">
-        <v>0.827730716400836</v>
+        <v>0.22969696969697</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Homicidio</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="B3">
-        <v>22360</v>
+        <v>263</v>
       </c>
       <c r="C3">
-        <v>0.0870062608709187</v>
+        <v>0.159393939393939</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amenaza</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B4">
-        <v>6090</v>
+        <v>262</v>
       </c>
       <c r="C4">
-        <v>0.0236971435019631</v>
+        <v>0.158787878787879</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Desaparición forzada</t>
+          <t>Cocorná</t>
         </is>
       </c>
       <c r="B5">
-        <v>4414</v>
+        <v>188</v>
       </c>
       <c r="C5">
-        <v>0.0171755650932127</v>
+        <v>0.113939393939394</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Abandono o despojo de tierras</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="B6">
-        <v>3729</v>
+        <v>185</v>
       </c>
       <c r="C6">
-        <v>0.0145101228438129</v>
+        <v>0.112121212121212</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pérdida de bienes muebles/inmuebles</t>
+          <t>San Rafael</t>
         </is>
       </c>
       <c r="B7">
-        <v>2767</v>
+        <v>171</v>
       </c>
       <c r="C7">
-        <v>0.0107668302249478</v>
+        <v>0.103636363636364</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Secuestro</t>
+          <t>Marinilla</t>
         </is>
       </c>
       <c r="B8">
-        <v>1385</v>
+        <v>52</v>
       </c>
       <c r="C8">
-        <v>0.00538925184732658</v>
+        <v>0.0315151515151515</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Acto terrorista/atentados/combates</t>
+          <t>Alejandría</t>
         </is>
       </c>
       <c r="B9">
-        <v>799</v>
+        <v>42</v>
       </c>
       <c r="C9">
-        <v>0.00310903409820501</v>
+        <v>0.0254545454545455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Delitos contra libertad/integridad sexual</t>
+          <t>San Vicente Ferrer</t>
         </is>
       </c>
       <c r="B10">
-        <v>592</v>
+        <v>37</v>
       </c>
       <c r="C10">
-        <v>0.00230356468853237</v>
+        <v>0.0224242424242424</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sin información</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="B11">
-        <v>591</v>
+        <v>34</v>
       </c>
       <c r="C11">
-        <v>0.00229967353196391</v>
+        <v>0.0206060606060606</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Minas antipersonal/MUSE</t>
+          <t>Peñol</t>
         </is>
       </c>
       <c r="B12">
-        <v>471</v>
+        <v>25</v>
       </c>
       <c r="C12">
-        <v>0.00183273474374788</v>
+        <v>0.0151515151515152</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lesiones personales psicológicas</t>
+          <t>Guatapé</t>
         </is>
       </c>
       <c r="B13">
-        <v>449</v>
+        <v>12</v>
       </c>
       <c r="C13">
-        <v>0.00174712929924161</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Lesiones personales físicas</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>298</v>
-      </c>
-      <c r="C14">
-        <v>0.00115956465740312</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Tortura</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>179</v>
-      </c>
-      <c r="C15">
-        <v>0.000696517025755565</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Vinculación de NNA a grupos armados</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>148</v>
-      </c>
-      <c r="C16">
-        <v>0.000575891172133093</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Confinamiento</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
+        <v>0.00727272727272727</v>
       </c>
     </row>
   </sheetData>
@@ -3165,185 +4083,143 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Código DANE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Municipio</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Homicidios por 100.000 hab.</t>
+      <c r="A1" s="121" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="121" t="inlineStr">
+        <is>
+          <t>victimas_ocurrencia</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>5021</v>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Alejandría</t>
         </is>
       </c>
-      <c r="C2">
-        <v>18.9214758751183</v>
+      <c r="B2">
+        <v>7678</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>5197</v>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Cocorná</t>
         </is>
       </c>
-      <c r="C3">
-        <v>24.8617067561688</v>
+      <c r="B3">
+        <v>39522</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>5206</v>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Concepción</t>
         </is>
       </c>
-      <c r="C4">
-        <v>39.1236306729264</v>
+      <c r="B4">
+        <v>4469</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>5313</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="C5">
-        <v>19.0276852820854</v>
+      <c r="B5">
+        <v>42239</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5321</v>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Guatapé</t>
         </is>
       </c>
-      <c r="C6">
-        <v>30.9437854564208</v>
+      <c r="B6">
+        <v>2915</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>5440</v>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Marinilla</t>
         </is>
       </c>
-      <c r="C7">
-        <v>33.6066675628445</v>
+      <c r="B7">
+        <v>7118</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>5541</v>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Peñol</t>
         </is>
       </c>
-      <c r="C8">
-        <v>41.9691946111554</v>
+      <c r="B8">
+        <v>7851</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>5649</v>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>San Carlos</t>
         </is>
       </c>
-      <c r="C9">
-        <v>11.8077695123391</v>
+      <c r="B9">
+        <v>46959</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>5652</v>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="C10">
-        <v>33.0141961043249</v>
+      <c r="B10">
+        <v>21242</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>5660</v>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>San Luis</t>
         </is>
       </c>
-      <c r="C11">
-        <v>62.2966705890496</v>
+      <c r="B11">
+        <v>36685</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>5667</v>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>San Rafael</t>
         </is>
       </c>
-      <c r="C12">
-        <v>22.9739819654242</v>
+      <c r="B12">
+        <v>28701</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>5674</v>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>San Vicente Ferrer</t>
         </is>
       </c>
-      <c r="C13">
-        <v>40.3616402970617</v>
+      <c r="B13">
+        <v>11614</v>
       </c>
     </row>
   </sheetData>
@@ -3358,394 +4234,394 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Hectáreas con permisos</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Hectáreas en tránsito</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Hectáreas ilícita</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Total EVOA (ha)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>POVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="13">
         <v>2018</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="14">
         <v>0</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="15">
         <v>0</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="16">
         <v>0</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>POVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="13">
         <v>2019</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="14">
         <v>0</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="15">
         <v>0</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="16">
         <v>0</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>POVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="13">
         <v>2020</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="14">
         <v>0</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="15">
         <v>0</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="16">
         <v>0</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN ORIENTE</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ORIENTE</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="13">
         <v>2018</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="14">
         <v>11.260776</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="15">
         <v>23.546906</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="16">
         <v>203.579819</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="17">
         <v>238.387501</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN ORIENTE</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>ORIENTE</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="13">
         <v>2019</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="14">
         <v>11.395777</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="15">
         <v>0</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="16">
         <v>273.813162</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="17">
         <v>285.208939</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN ORIENTE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ORIENTE</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="13">
         <v>2020</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="14">
         <v>130.516064</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="15">
         <v>21.849043</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="16">
         <v>133.541332</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="17">
         <v>285.906439</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="13">
         <v>2018</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="14">
         <v>16186.547037</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="15">
         <v>1633.054856</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="16">
         <v>18627.422655</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="17">
         <v>36447.024548</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="13">
         <v>2019</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="14">
         <v>17799.238713</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="15">
         <v>1658.203768</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="16">
         <v>20744.042756</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="17">
         <v>40201.485237</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="13">
         <v>2020</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="14">
         <v>19240.998973</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="15">
         <v>1806.249069</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="16">
         <v>19842.333019</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="17">
         <v>40889.581061</v>
       </c>
     </row>
@@ -3758,26 +4634,1142 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="123" t="inlineStr">
+        <is>
+          <t>hecho</t>
+        </is>
+      </c>
+      <c r="B1" s="123" t="inlineStr">
+        <is>
+          <t>victimas_ocurrencia</t>
+        </is>
+      </c>
+      <c r="C1" s="123" t="inlineStr">
+        <is>
+          <t>proporcion_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Desplazamiento forzado</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>212721</v>
+      </c>
+      <c r="C2">
+        <v>0.827730716400836</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Homicidio</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>22360</v>
+      </c>
+      <c r="C3">
+        <v>0.0870062608709187</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Amenaza</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>6090</v>
+      </c>
+      <c r="C4">
+        <v>0.0236971435019631</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Desaparición forzada</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>4414</v>
+      </c>
+      <c r="C5">
+        <v>0.0171755650932127</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Abandono o despojo de tierras</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>3729</v>
+      </c>
+      <c r="C6">
+        <v>0.0145101228438129</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Pérdida de bienes muebles/inmuebles</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2767</v>
+      </c>
+      <c r="C7">
+        <v>0.0107668302249478</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Secuestro</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>1385</v>
+      </c>
+      <c r="C8">
+        <v>0.00538925184732658</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Acto terrorista/atentados/combates</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>799</v>
+      </c>
+      <c r="C9">
+        <v>0.00310903409820501</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Delitos contra libertad/integridad sexual</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>592</v>
+      </c>
+      <c r="C10">
+        <v>0.00230356468853237</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>591</v>
+      </c>
+      <c r="C11">
+        <v>0.00229967353196391</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Minas antipersonal/MUSE</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>471</v>
+      </c>
+      <c r="C12">
+        <v>0.00183273474374788</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lesiones personales psicológicas</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>449</v>
+      </c>
+      <c r="C13">
+        <v>0.00174712929924161</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lesiones personales físicas</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>298</v>
+      </c>
+      <c r="C14">
+        <v>0.00115956465740312</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tortura</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>179</v>
+      </c>
+      <c r="C15">
+        <v>0.000696517025755565</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vinculación de NNA a grupos armados</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>148</v>
+      </c>
+      <c r="C16">
+        <v>0.000575891172133093</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Confinamiento</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="2.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="125" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="125" t="inlineStr">
+        <is>
+          <t>estado_fase</t>
+        </is>
+      </c>
+      <c r="C1" s="125" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alejandría</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Alejandría</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Alejandría</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Alejandría</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alejandría</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Alejandría</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Alejandría</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="127" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="127" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="127" t="inlineStr">
         <is>
           <t>Homicidios por 100.000 hab.</t>
         </is>
@@ -3785,561 +5777,1362 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>5004</v>
+        <v>5021</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abriaquí</t>
+          <t>Alejandría</t>
         </is>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>18.9214758751183</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>5138</v>
+        <v>5197</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cañasgordas</t>
+          <t>Cocorná</t>
         </is>
       </c>
       <c r="C3">
-        <v>38.7847446670976</v>
+        <v>24.8617067561688</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>5234</v>
+        <v>5206</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dabeiba</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="C4">
-        <v>52.4024508223154</v>
+        <v>39.1236306729264</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>5284</v>
+        <v>5313</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Frontino</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="C5">
-        <v>32.1425291578657</v>
+        <v>19.0276852820854</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>5543</v>
+        <v>5321</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Peque</t>
+          <t>Guatapé</t>
         </is>
       </c>
       <c r="C6">
-        <v>11.3869278068777</v>
+        <v>30.9437854564208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5842</v>
+        <v>5440</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Uramita</t>
+          <t>Marinilla</t>
         </is>
       </c>
       <c r="C7">
-        <v>13.4138162307176</v>
+        <v>33.6066675628445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>5038</v>
+        <v>5541</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Angostura</t>
+          <t>Peñol</t>
         </is>
       </c>
       <c r="C8">
-        <v>55.9507633282711</v>
+        <v>41.9691946111554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>5040</v>
+        <v>5649</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Anorí</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="C9">
-        <v>218.683147135726</v>
+        <v>11.8077695123391</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>5107</v>
+        <v>5652</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Briceño</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="C10">
-        <v>226.21591051904</v>
+        <v>33.0141961043249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>5134</v>
+        <v>5660</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Campamento</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="C11">
-        <v>99.9500249875062</v>
+        <v>62.2966705890496</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>5150</v>
+        <v>5667</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carolina del Príncipe</t>
+          <t>San Rafael</t>
         </is>
       </c>
       <c r="C12">
-        <v>76.103500761035</v>
+        <v>22.9739819654242</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>5315</v>
+        <v>5674</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Guadalupe</t>
+          <t>San Vicente Ferrer</t>
         </is>
       </c>
       <c r="C13">
-        <v>42.8021115708375</v>
+        <v>40.3616402970617</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="129" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="129" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="129" t="inlineStr">
+        <is>
+          <t>Homicidios por 100.000 hab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>5001</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>13.1706813513831</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>5002</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Abejorral</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>28.3728188395517</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>5004</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Abriaquí</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>5021</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alejandría</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>18.9214758751183</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5030</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Amagá</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>36.5207864142675</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>5031</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>113.581606663454</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5034</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Andes</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>147.684440231887</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5036</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Angelópolis</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>48.363694986297</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5038</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>55.9507633282711</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5040</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>218.683147135726</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>5042</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>31.6667253087506</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>5044</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Anzá</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>52.0765525322224</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>5310</v>
+        <v>5055</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gómez Plata</t>
+          <t>Argelia</t>
         </is>
       </c>
       <c r="C14">
-        <v>57.8424756579582</v>
+        <v>12.1728545343883</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>5361</v>
+        <v>5079</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ituango</t>
+          <t>Barbosa</t>
         </is>
       </c>
       <c r="C15">
-        <v>71.15026257835</v>
+        <v>17.3351193759357</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>5647</v>
+        <v>5086</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>San Andrés de Cuerquía</t>
+          <t>Belmira</t>
         </is>
       </c>
       <c r="C16">
-        <v>391.786003782761</v>
+        <v>81.2875955129247</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>5658</v>
+        <v>5088</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>San José de la Montaña</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="C17">
-        <v>74.6825989544436</v>
+        <v>7.64226237548096</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>5819</v>
+        <v>5091</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>Betania</t>
         </is>
       </c>
       <c r="C18">
-        <v>124.378109452736</v>
+        <v>176.727746256162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>5854</v>
+        <v>5093</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Betulia</t>
         </is>
       </c>
       <c r="C19">
-        <v>126.548554682297</v>
+        <v>206.124852767962</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>5887</v>
+        <v>5101</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yarumal</t>
+          <t>Ciudad Bolívar</t>
         </is>
       </c>
       <c r="C20">
-        <v>59.6886639289466</v>
+        <v>137.815979400138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>5086</v>
+        <v>5107</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Belmira</t>
+          <t>Briceño</t>
         </is>
       </c>
       <c r="C21">
-        <v>81.2875955129247</v>
+        <v>226.21591051904</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>5237</v>
+        <v>5113</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Donmatías</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="C22">
-        <v>25.2614560703279</v>
+        <v>90.7852927825692</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>5264</v>
+        <v>5125</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Entrerríos</t>
+          <t>Caicedo</t>
         </is>
       </c>
       <c r="C23">
-        <v>15.7035175879397</v>
+        <v>32.9416932030306</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>5664</v>
+        <v>5129</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>San Pedro de los Milagros</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="C24">
-        <v>31.4084443846188</v>
+        <v>12.3495599065924</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>5686</v>
+        <v>5134</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Santa Rosa de Osos</t>
+          <t>Campamento</t>
         </is>
       </c>
       <c r="C25">
-        <v>22.3541392414495</v>
+        <v>99.9500249875062</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>5113</v>
+        <v>5138</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Buriticá</t>
+          <t>Cañasgordas</t>
         </is>
       </c>
       <c r="C26">
-        <v>90.7852927825692</v>
+        <v>38.7847446670976</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>5240</v>
+        <v>5145</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ebéjico</t>
+          <t>Caramanta</t>
         </is>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>22.2271615914648</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>5306</v>
+        <v>5150</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>Carolina del Príncipe</t>
         </is>
       </c>
       <c r="C28">
-        <v>15.6152404747033</v>
+        <v>76.103500761035</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>5347</v>
+        <v>5197</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>Cocorná</t>
         </is>
       </c>
       <c r="C29">
-        <v>39.6982929734021</v>
+        <v>24.8617067561688</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>5501</v>
+        <v>5206</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Olaya</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>39.1236306729264</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>5628</v>
+        <v>5209</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>Concordia</t>
         </is>
       </c>
       <c r="C31">
-        <v>80.7346856393178</v>
+        <v>99.2645399990976</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>5656</v>
+        <v>5212</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>San Jerónimo</t>
+          <t>Copacabana</t>
         </is>
       </c>
       <c r="C32">
-        <v>81.7661488143908</v>
+        <v>16.5049184657028</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>5021</v>
+        <v>5234</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Alejandría</t>
+          <t>Dabeiba</t>
         </is>
       </c>
       <c r="C33">
-        <v>18.9214758751183</v>
+        <v>52.4024508223154</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>5197</v>
+        <v>5237</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cocorná</t>
+          <t>Donmatías</t>
         </is>
       </c>
       <c r="C34">
-        <v>24.8617067561688</v>
+        <v>25.2614560703279</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>5206</v>
+        <v>5240</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Ebéjico</t>
         </is>
       </c>
       <c r="C35">
-        <v>39.1236306729264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>5313</v>
+        <v>5264</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Entrerríos</t>
         </is>
       </c>
       <c r="C36">
-        <v>19.0276852820854</v>
+        <v>15.7035175879397</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>5321</v>
+        <v>5266</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Guatapé</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="C37">
-        <v>30.9437854564208</v>
+        <v>3.02300887630981</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>5440</v>
+        <v>5282</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Marinilla</t>
+          <t>Fredonia</t>
         </is>
       </c>
       <c r="C38">
-        <v>33.6066675628445</v>
+        <v>22.7264118783379</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>5541</v>
+        <v>5284</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Peñol</t>
+          <t>Frontino</t>
         </is>
       </c>
       <c r="C39">
-        <v>41.9691946111554</v>
+        <v>32.1425291578657</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>5649</v>
+        <v>5306</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Giraldo</t>
         </is>
       </c>
       <c r="C40">
-        <v>11.8077695123391</v>
+        <v>15.6152404747033</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>5652</v>
+        <v>5308</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Girardota</t>
         </is>
       </c>
       <c r="C41">
-        <v>33.0141961043249</v>
+        <v>4.88289197415322</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>5660</v>
+        <v>5310</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Gómez Plata</t>
         </is>
       </c>
       <c r="C42">
-        <v>62.2966705890496</v>
+        <v>57.8424756579582</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>5667</v>
+        <v>5313</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>San Rafael</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="C43">
-        <v>22.9739819654242</v>
+        <v>19.0276852820854</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
+        <v>5315</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>42.8021115708375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>5321</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Guatapé</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>30.9437854564208</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>5347</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>39.6982929734021</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>5353</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Hispania</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>168.662506324844</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>5360</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Itagüí</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>3.61215918457148</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>5361</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>71.15026257835</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>5364</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Jardín</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>71.2758374910905</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>5368</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Jericó</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>69.5603784084585</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>5380</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>9.62822997027284</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>5390</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>La Pintada</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>80.887450889762</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>5400</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>70.6655027642682</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>5440</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>33.6066675628445</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>5467</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Montebello</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>45.8855919241358</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>5483</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>63.6363636363636</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>5501</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>5541</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Peñol</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>41.9691946111554</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>5543</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Peque</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>11.3869278068777</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>5576</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pueblorrico</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>99.41455870982</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>5604</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>118.106659398565</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>5628</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>80.7346856393178</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>5631</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>2.81288677193114</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>5642</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Salgar</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>100.396301188904</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>5647</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>391.786003782761</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>5649</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>11.8077695123391</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>5652</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>33.0141961043249</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>5656</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>81.7661488143908</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>5658</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>74.6825989544436</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>5660</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>62.2966705890496</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>5664</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>San Pedro de los Milagros</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>31.4084443846188</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>5667</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>22.9739819654242</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
         <v>5674</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>San Vicente Ferrer</t>
         </is>
       </c>
-      <c r="C44">
+      <c r="C74">
         <v>40.3616402970617</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>5679</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>33.9328130302002</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>5686</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Osos</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>22.3541392414495</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>5736</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>66.0854535749689</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>5756</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>38.9105058365759</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>5789</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Támesis</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>5.99736116108912</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>5792</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tarso</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>76.2660158633313</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>5809</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Titiribí</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>60.6743520845974</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>5819</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>124.378109452736</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>5842</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Uramita</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>13.4138162307176</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>5847</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>96.9113417531574</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>5854</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>126.548554682297</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>5856</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>14.8942508191838</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>5858</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>41.1184210526316</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>5861</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Venecia</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>40.2835965194973</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>5885</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Yalí</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>25.9100919808265</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>5887</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>59.6886639289466</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>5890</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Yolombó</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>31.9514338205927</v>
       </c>
     </row>
   </sheetData>
@@ -4354,47 +7147,47 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>Hurtos por 100.000 hab.</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>Homicidios por 100.000 hab.</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="19" t="inlineStr">
         <is>
           <t>Violencia intrafamiliar por 100.000 hab.</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="19" t="inlineStr">
         <is>
           <t>Delitos sexuales por 100.000 hab.</t>
         </is>
@@ -4414,16 +7207,16 @@
           <t>ORIENTE</t>
         </is>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="21">
         <v>37.8429517502365</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="23">
         <v>18.9214758751183</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="25">
         <v>245.979186376537</v>
       </c>
-      <c r="G2" s="21">
+      <c r="G2" s="27">
         <v>113.52885525071</v>
       </c>
     </row>
@@ -4441,16 +7234,16 @@
           <t>ORIENTE</t>
         </is>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="21">
         <v>99.4468270246752</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="23">
         <v>24.8617067561688</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="25">
         <v>186.462800671266</v>
       </c>
-      <c r="G3" s="21">
+      <c r="G3" s="27">
         <v>80.8005469575486</v>
       </c>
     </row>
@@ -4468,16 +7261,16 @@
           <t>ORIENTE</t>
         </is>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="21">
         <v>97.8090766823161</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="23">
         <v>39.1236306729264</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="25">
         <v>78.2472613458529</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="27">
         <v>78.2472613458529</v>
       </c>
     </row>
@@ -4495,16 +7288,16 @@
           <t>ORIENTE</t>
         </is>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="21">
         <v>76.1107411283417</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="23">
         <v>19.0276852820854</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="25">
         <v>152.221482256683</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="27">
         <v>123.679954333555</v>
       </c>
     </row>
@@ -4522,16 +7315,16 @@
           <t>ORIENTE</t>
         </is>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="21">
         <v>412.583806085611</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="23">
         <v>30.9437854564208</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="25">
         <v>453.842186694172</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="27">
         <v>61.8875709128417</v>
       </c>
     </row>
@@ -4549,16 +7342,16 @@
           <t>ORIENTE</t>
         </is>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="21">
         <v>131.73813684635</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="23">
         <v>33.6066675628445</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="25">
         <v>20.1640005377067</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="27">
         <v>8.06560021508267</v>
       </c>
     </row>
@@ -4576,16 +7369,16 @@
           <t>ORIENTE</t>
         </is>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="21">
         <v>180.467536827968</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="23">
         <v>41.9691946111554</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="25">
         <v>83.9383892223108</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="27">
         <v>71.3476308389642</v>
       </c>
     </row>
@@ -4603,16 +7396,16 @@
           <t>ORIENTE</t>
         </is>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="21">
         <v>118.077695123391</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="23">
         <v>11.8077695123391</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="25">
         <v>123.981579879561</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="27">
         <v>94.462156098713</v>
       </c>
     </row>
@@ -4630,16 +7423,16 @@
           <t>ORIENTE</t>
         </is>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="21">
         <v>16.5070980521624</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="23">
         <v>33.0141961043249</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="25">
         <v>49.5212941564873</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="27">
         <v>33.0141961043249</v>
       </c>
     </row>
@@ -4657,16 +7450,16 @@
           <t>ORIENTE</t>
         </is>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="21">
         <v>166.124454904132</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="23">
         <v>62.2966705890496</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="25">
         <v>131.515193465771</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="27">
         <v>83.0622274520662</v>
       </c>
     </row>
@@ -4684,16 +7477,16 @@
           <t>ORIENTE</t>
         </is>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="21">
         <v>103.382918844409</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="23">
         <v>22.9739819654242</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="25">
         <v>34.4609729481362</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="27">
         <v>0</v>
       </c>
     </row>
@@ -4711,103 +7504,103 @@
           <t>ORIENTE</t>
         </is>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="21">
         <v>108.976428802067</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="23">
         <v>40.3616402970617</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="25">
         <v>96.867936712948</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="27">
         <v>36.3254762673555</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="22">
         <v>134.497793256405</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="24">
         <v>32.9564129171324</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="26">
         <v>95.7517402322091</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="28">
         <v>46.3171208565104</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN ORIENTE</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>ORIENTE</t>
-        </is>
-      </c>
-      <c r="D15" s="16">
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D15" s="22">
         <v>243.249978790193</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="24">
         <v>29.030923899211</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="26">
         <v>168.352846356155</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="28">
         <v>54.0850089081191</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="22">
         <v>506.74242087463</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="24">
         <v>25.3306260114209</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="26">
         <v>276.471875355423</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="28">
         <v>71.9216577862736</v>
       </c>
     </row>
@@ -4823,59 +7616,59 @@
   <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Víctimas por ocurrencia</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>Víctimas por declaración</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>Víctimas por ubicación</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="30" t="inlineStr">
         <is>
           <t>Sujetos de atención</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="30" t="inlineStr">
         <is>
           <t>Eventos</t>
         </is>
@@ -4900,19 +7693,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="32">
         <v>7678</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="34">
         <v>5966</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="36">
         <v>3703</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="38">
         <v>3303</v>
       </c>
-      <c r="I2" s="31">
+      <c r="I2" s="40">
         <v>8514</v>
       </c>
     </row>
@@ -4935,19 +7728,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="32">
         <v>39522</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="34">
         <v>20915</v>
       </c>
-      <c r="G3" s="27">
+      <c r="G3" s="36">
         <v>15255</v>
       </c>
-      <c r="H3" s="29">
+      <c r="H3" s="38">
         <v>13910</v>
       </c>
-      <c r="I3" s="31">
+      <c r="I3" s="40">
         <v>44473</v>
       </c>
     </row>
@@ -4970,19 +7763,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="32">
         <v>4469</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="34">
         <v>2487</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="36">
         <v>1704</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="38">
         <v>1385</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="40">
         <v>4860</v>
       </c>
     </row>
@@ -5005,19 +7798,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="32">
         <v>42239</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="34">
         <v>23973</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="36">
         <v>10943</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="38">
         <v>9957</v>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="40">
         <v>47490</v>
       </c>
     </row>
@@ -5040,19 +7833,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="32">
         <v>2915</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="34">
         <v>3260</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="36">
         <v>2785</v>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="38">
         <v>2177</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="40">
         <v>3105</v>
       </c>
     </row>
@@ -5075,19 +7868,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="32">
         <v>7118</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="34">
         <v>13334</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="36">
         <v>14266</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="38">
         <v>12516</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="40">
         <v>7426</v>
       </c>
     </row>
@@ -5110,19 +7903,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="32">
         <v>7851</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="34">
         <v>5694</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="36">
         <v>5418</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="38">
         <v>4514</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="40">
         <v>8140</v>
       </c>
     </row>
@@ -5145,19 +7938,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="32">
         <v>46959</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="34">
         <v>17843</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="36">
         <v>15963</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="38">
         <v>14402</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="40">
         <v>51944</v>
       </c>
     </row>
@@ -5180,19 +7973,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="32">
         <v>21242</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="34">
         <v>9793</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="36">
         <v>6667</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="38">
         <v>6048</v>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="40">
         <v>25539</v>
       </c>
     </row>
@@ -5215,19 +8008,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="32">
         <v>36685</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="34">
         <v>23474</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="36">
         <v>13361</v>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="38">
         <v>11980</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="40">
         <v>40589</v>
       </c>
     </row>
@@ -5250,19 +8043,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="32">
         <v>28701</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="34">
         <v>18831</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="36">
         <v>14759</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="38">
         <v>13399</v>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="40">
         <v>35094</v>
       </c>
     </row>
@@ -5285,56 +8078,56 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="32">
         <v>11614</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="34">
         <v>8469</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="36">
         <v>3026</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="38">
         <v>2391</v>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="40">
         <v>12080</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="31" t="inlineStr">
         <is>
           <t>POVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="33">
         <v>256993</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="35">
         <v>154039</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="37">
         <v>107850</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="39">
         <v>95982</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="41">
         <v>289254</v>
       </c>
     </row>
@@ -5350,23 +8143,23 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="87.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="88.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Hecho victimizante</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="43" t="inlineStr">
         <is>
           <t>Víctimas por ocurrencia</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="43" t="inlineStr">
         <is>
           <t>Proporción sobre el total (%)</t>
         </is>
@@ -5378,10 +8171,10 @@
           <t>Desplazamiento forzado</t>
         </is>
       </c>
-      <c r="B2" s="33">
+      <c r="B2" s="44">
         <v>212721</v>
       </c>
-      <c r="C2" s="34">
+      <c r="C2" s="45">
         <v>0.827730716400836</v>
       </c>
     </row>
@@ -5391,10 +8184,10 @@
           <t>Homicidio (Conflicto)</t>
         </is>
       </c>
-      <c r="B3" s="33">
+      <c r="B3" s="44">
         <v>22360</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="45">
         <v>0.0870062608709187</v>
       </c>
     </row>
@@ -5404,10 +8197,10 @@
           <t>Amenaza (Conflicto)</t>
         </is>
       </c>
-      <c r="B4" s="33">
+      <c r="B4" s="44">
         <v>6090</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="45">
         <v>0.0236971435019631</v>
       </c>
     </row>
@@ -5417,10 +8210,10 @@
           <t>Desaparición forzada</t>
         </is>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="44">
         <v>4414</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="45">
         <v>0.0171755650932127</v>
       </c>
     </row>
@@ -5430,10 +8223,10 @@
           <t>Abandono o Despojo Forzado de Tierras</t>
         </is>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="44">
         <v>3729</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="45">
         <v>0.0145101228438129</v>
       </c>
     </row>
@@ -5443,10 +8236,10 @@
           <t>Perdida de Bienes Muebles o Inmuebles</t>
         </is>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="44">
         <v>2767</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="45">
         <v>0.0107668302249478</v>
       </c>
     </row>
@@ -5456,10 +8249,10 @@
           <t>Secuestro (Conflicto)</t>
         </is>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="44">
         <v>1385</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="45">
         <v>0.00538925184732658</v>
       </c>
     </row>
@@ -5469,10 +8262,10 @@
           <t>Acto terrorista / Atentados / Combates / Enfrentamientos / Hostigamientos</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="44">
         <v>799</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="45">
         <v>0.00310903409820501</v>
       </c>
     </row>
@@ -5482,10 +8275,10 @@
           <t>Delitos contra la libertad y la integridad sexual en desarrollo del conflicto armado</t>
         </is>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="44">
         <v>592</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="45">
         <v>0.00230356468853237</v>
       </c>
     </row>
@@ -5495,10 +8288,10 @@
           <t>Sin informacion (Conflicto)</t>
         </is>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="44">
         <v>591</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="45">
         <v>0.00229967353196391</v>
       </c>
     </row>
@@ -5508,10 +8301,10 @@
           <t>Minas Antipersonal, Munición sin Explotar y Artefacto Explosivo improvisado</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="44">
         <v>471</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="45">
         <v>0.00183273474374788</v>
       </c>
     </row>
@@ -5521,10 +8314,10 @@
           <t>Lesiones Personales Psicologicas</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="44">
         <v>449</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="45">
         <v>0.00174712929924161</v>
       </c>
     </row>
@@ -5534,10 +8327,10 @@
           <t>Lesiones Personales Fisicas</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="44">
         <v>298</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="45">
         <v>0.00115956465740312</v>
       </c>
     </row>
@@ -5547,10 +8340,10 @@
           <t>Tortura (Conflicto)</t>
         </is>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="44">
         <v>179</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="45">
         <v>0.000696517025755565</v>
       </c>
     </row>
@@ -5560,10 +8353,10 @@
           <t>Vinculación de Niños Niñas y Adolescentes a Actividades Relacionadas con grupos armados</t>
         </is>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="44">
         <v>148</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="45">
         <v>0.000575891172133093</v>
       </c>
     </row>
@@ -5573,10 +8366,10 @@
           <t>Confinamiento (Conflicto)</t>
         </is>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="44">
         <v>0</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="45">
         <v>0</v>
       </c>
     </row>
@@ -5586,10 +8379,10 @@
           <t>TOTAL PROVINCIA AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="B18" s="33">
+      <c r="B18" s="44">
         <v>256993</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="45">
         <v>1</v>
       </c>
     </row>
@@ -5605,47 +8398,47 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="47" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="47" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="47" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="47" t="inlineStr">
         <is>
           <t>Número de solicitudes</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="47" t="inlineStr">
         <is>
           <t>Número de predios</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="47" t="inlineStr">
         <is>
           <t>Número de titulares</t>
         </is>
@@ -5670,13 +8463,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="49">
         <v>47</v>
       </c>
-      <c r="F2" s="37">
+      <c r="F2" s="51">
         <v>44</v>
       </c>
-      <c r="G2" s="39">
+      <c r="G2" s="53">
         <v>36</v>
       </c>
     </row>
@@ -5699,13 +8492,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="49">
         <v>352</v>
       </c>
-      <c r="F3" s="37">
+      <c r="F3" s="51">
         <v>306</v>
       </c>
-      <c r="G3" s="39">
+      <c r="G3" s="53">
         <v>302</v>
       </c>
     </row>
@@ -5728,13 +8521,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="49">
         <v>37</v>
       </c>
-      <c r="F4" s="37">
+      <c r="F4" s="51">
         <v>37</v>
       </c>
-      <c r="G4" s="39">
+      <c r="G4" s="53">
         <v>31</v>
       </c>
     </row>
@@ -5757,13 +8550,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="49">
         <v>1390</v>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="51">
         <v>1365</v>
       </c>
-      <c r="G5" s="39">
+      <c r="G5" s="53">
         <v>1076</v>
       </c>
     </row>
@@ -5786,13 +8579,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="49">
         <v>23</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="51">
         <v>22</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="53">
         <v>20</v>
       </c>
     </row>
@@ -5815,13 +8608,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="49">
         <v>12</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="51">
         <v>12</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="53">
         <v>11</v>
       </c>
     </row>
@@ -5844,13 +8637,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="49">
         <v>39</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="51">
         <v>29</v>
       </c>
-      <c r="G8" s="39">
+      <c r="G8" s="53">
         <v>35</v>
       </c>
     </row>
@@ -5873,13 +8666,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="49">
         <v>2112</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="51">
         <v>1977</v>
       </c>
-      <c r="G9" s="39">
+      <c r="G9" s="53">
         <v>1744</v>
       </c>
     </row>
@@ -5902,13 +8695,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="49">
         <v>257</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="51">
         <v>238</v>
       </c>
-      <c r="G10" s="39">
+      <c r="G10" s="53">
         <v>216</v>
       </c>
     </row>
@@ -5931,13 +8724,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="49">
         <v>437</v>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="51">
         <v>378</v>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="53">
         <v>399</v>
       </c>
     </row>
@@ -5960,13 +8753,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="49">
         <v>403</v>
       </c>
-      <c r="F12" s="37">
+      <c r="F12" s="51">
         <v>294</v>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="53">
         <v>328</v>
       </c>
     </row>
@@ -5989,106 +8782,106 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="49">
         <v>32</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="51">
         <v>25</v>
       </c>
-      <c r="G13" s="39">
+      <c r="G13" s="53">
         <v>29</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="48" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="48" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="48" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="48" t="inlineStr">
         <is>
           <t>POVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="50">
         <v>5141</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="52">
         <v>4727</v>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="54">
         <v>4227</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="48" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN ORIENTE</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>ORIENTE</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="C15" s="48" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="50">
         <v>6932</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="52">
         <v>6165</v>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="54">
         <v>5749</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="48" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="48" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="48" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="50">
         <v>27352</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="52">
         <v>24834</v>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="54">
         <v>23637</v>
       </c>
     </row>
@@ -6104,47 +8897,47 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="56" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="56" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="56" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="56" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="56" t="inlineStr">
         <is>
           <t>Número de solicitudes</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="56" t="inlineStr">
         <is>
           <t>Población (2025)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="56" t="inlineStr">
         <is>
           <t>Tasa de solicitudes (por 1.000 hab.)</t>
         </is>
@@ -6169,13 +8962,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="41">
+      <c r="E2" s="58">
         <v>47</v>
       </c>
-      <c r="F2" s="43">
+      <c r="F2" s="60">
         <v>5285</v>
       </c>
-      <c r="G2" s="45">
+      <c r="G2" s="62">
         <v>8.89309366130558</v>
       </c>
     </row>
@@ -6198,13 +8991,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="41">
+      <c r="E3" s="58">
         <v>352</v>
       </c>
-      <c r="F3" s="43">
+      <c r="F3" s="60">
         <v>16089</v>
       </c>
-      <c r="G3" s="45">
+      <c r="G3" s="62">
         <v>21.8783019454286</v>
       </c>
     </row>
@@ -6227,13 +9020,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="41">
+      <c r="E4" s="58">
         <v>37</v>
       </c>
-      <c r="F4" s="43">
+      <c r="F4" s="60">
         <v>5112</v>
       </c>
-      <c r="G4" s="45">
+      <c r="G4" s="62">
         <v>7.23787167449139</v>
       </c>
     </row>
@@ -6256,13 +9049,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="58">
         <v>1390</v>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="60">
         <v>10511</v>
       </c>
-      <c r="G5" s="45">
+      <c r="G5" s="62">
         <v>132.242412710494</v>
       </c>
     </row>
@@ -6285,13 +9078,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="58">
         <v>23</v>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="60">
         <v>9695</v>
       </c>
-      <c r="G6" s="45">
+      <c r="G6" s="62">
         <v>2.37235688499226</v>
       </c>
     </row>
@@ -6314,13 +9107,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="58">
         <v>12</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="60">
         <v>74390</v>
       </c>
-      <c r="G7" s="45">
+      <c r="G7" s="62">
         <v>0.161312004301653</v>
       </c>
     </row>
@@ -6343,13 +9136,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="58">
         <v>39</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="60">
         <v>23827</v>
       </c>
-      <c r="G8" s="45">
+      <c r="G8" s="62">
         <v>1.63679858983506</v>
       </c>
     </row>
@@ -6372,13 +9165,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="58">
         <v>2112</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="60">
         <v>16938</v>
       </c>
-      <c r="G9" s="45">
+      <c r="G9" s="62">
         <v>124.690046050301</v>
       </c>
     </row>
@@ -6401,13 +9194,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="58">
         <v>257</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="60">
         <v>6058</v>
       </c>
-      <c r="G10" s="45">
+      <c r="G10" s="62">
         <v>42.4232419940574</v>
       </c>
     </row>
@@ -6430,13 +9223,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="58">
         <v>437</v>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="60">
         <v>14447</v>
       </c>
-      <c r="G11" s="45">
+      <c r="G11" s="62">
         <v>30.2484944971274</v>
       </c>
     </row>
@@ -6459,13 +9252,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="58">
         <v>403</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="60">
         <v>17411</v>
       </c>
-      <c r="G12" s="45">
+      <c r="G12" s="62">
         <v>23.1462868301648</v>
       </c>
     </row>
@@ -6488,106 +9281,106 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="58">
         <v>32</v>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="60">
         <v>24776</v>
       </c>
-      <c r="G13" s="45">
+      <c r="G13" s="62">
         <v>1.29157248950597</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="57" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="57" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="57" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="57" t="inlineStr">
         <is>
           <t>POVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="59">
         <v>5141</v>
       </c>
-      <c r="F14" s="44">
+      <c r="F14" s="61">
         <v>224539</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="63">
         <v>22.8957998387808</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="57" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="57" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN ORIENTE</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>ORIENTE</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="C15" s="57" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D15" s="57" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="59">
         <v>6932</v>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="61">
         <v>754368</v>
       </c>
-      <c r="G15" s="46">
+      <c r="G15" s="63">
         <v>9.18914906252651</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="57" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="57" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="57" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="57" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="59">
         <v>27352</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="61">
         <v>6821720</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="63">
         <v>4.00954597960632</v>
       </c>
     </row>
@@ -6603,46 +9396,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="5" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="65" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="65" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="65" t="inlineStr">
         <is>
           <t>Muy seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="65" t="inlineStr">
         <is>
           <t>Seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="65" t="inlineStr">
         <is>
           <t>Inseguro (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="65" t="inlineStr">
         <is>
           <t>Muy inseguro (%)</t>
         </is>
@@ -6659,19 +9453,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="51">
+      <c r="C2" s="70">
         <v>424</v>
       </c>
-      <c r="D2" s="47">
+      <c r="D2" s="66">
         <v>0.0762291157122858</v>
       </c>
-      <c r="E2" s="48">
+      <c r="E2" s="67">
         <v>0.796909107548368</v>
       </c>
-      <c r="F2" s="49">
+      <c r="F2" s="68">
         <v>0.102405484147952</v>
       </c>
-      <c r="G2" s="50">
+      <c r="G2" s="69">
         <v>0.0244562925913938</v>
       </c>
     </row>
@@ -6686,19 +9480,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="51">
+      <c r="C3" s="70">
         <v>424</v>
       </c>
-      <c r="D3" s="47">
+      <c r="D3" s="66">
         <v>0.131890385830109</v>
       </c>
-      <c r="E3" s="48">
+      <c r="E3" s="67">
         <v>0.732835979857508</v>
       </c>
-      <c r="F3" s="49">
+      <c r="F3" s="68">
         <v>0.122990596265882</v>
       </c>
-      <c r="G3" s="50">
+      <c r="G3" s="69">
         <v>0.012283038046501</v>
       </c>
     </row>
@@ -6713,19 +9507,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="51">
+      <c r="C4" s="70">
         <v>424</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="66">
         <v>0.105702753690602</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="67">
         <v>0.746416340974337</v>
       </c>
-      <c r="F4" s="49">
+      <c r="F4" s="68">
         <v>0.135368719428366</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="69">
         <v>0.0125121859066946</v>
       </c>
     </row>
@@ -6740,19 +9534,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="51">
+      <c r="C5" s="70">
         <v>424</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="66">
         <v>0.118449195497242</v>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="67">
         <v>0.706848232801002</v>
       </c>
-      <c r="F5" s="49">
+      <c r="F5" s="68">
         <v>0.150803568894413</v>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="69">
         <v>0.0238990028073431</v>
       </c>
     </row>
@@ -6767,19 +9561,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="51">
+      <c r="C6" s="70">
         <v>416</v>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="66">
         <v>0.125765669333109</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="67">
         <v>0.716435928740168</v>
       </c>
-      <c r="F6" s="49">
+      <c r="F6" s="68">
         <v>0.142102055161066</v>
       </c>
-      <c r="G6" s="50">
+      <c r="G6" s="69">
         <v>0.0156963467656576</v>
       </c>
     </row>
@@ -6794,19 +9588,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="70">
         <v>920</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="66">
         <v>0.0989177034572841</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="67">
         <v>0.646739044103111</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="68">
         <v>0.217521794884898</v>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="69">
         <v>0.0368214575547076</v>
       </c>
     </row>
@@ -6821,19 +9615,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="70">
         <v>352</v>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="66">
         <v>0.0897220220375501</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="67">
         <v>0.739074974273691</v>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="68">
         <v>0.158568412350332</v>
       </c>
-      <c r="G8" s="50">
+      <c r="G8" s="69">
         <v>0.0126345913384268</v>
       </c>
     </row>
@@ -6848,19 +9642,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="70">
         <v>365</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="66">
         <v>0.0920788634174694</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="67">
         <v>0.741861820233017</v>
       </c>
-      <c r="F9" s="49">
+      <c r="F9" s="68">
         <v>0.145144896418472</v>
       </c>
-      <c r="G9" s="50">
+      <c r="G9" s="69">
         <v>0.0209144199310414</v>
       </c>
     </row>
@@ -6876,47 +9670,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="72" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="72" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="72" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="72" t="inlineStr">
         <is>
           <t>Más seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="72" t="inlineStr">
         <is>
           <t>Menos seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="72" t="inlineStr">
         <is>
           <t>Igual (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="72" t="inlineStr">
         <is>
           <t>No sabe/No responde (%)</t>
         </is>
@@ -6933,19 +9727,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="56">
+      <c r="C2" s="77">
         <v>424</v>
       </c>
-      <c r="D2" s="52">
+      <c r="D2" s="73">
         <v>0.140484986736131</v>
       </c>
-      <c r="E2" s="53">
+      <c r="E2" s="74">
         <v>0.0879232322824177</v>
       </c>
-      <c r="F2" s="54">
+      <c r="F2" s="75">
         <v>0.74625434938323</v>
       </c>
-      <c r="G2" s="55">
+      <c r="G2" s="76">
         <v>0.0253374315982208</v>
       </c>
     </row>
@@ -6960,19 +9754,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="56">
+      <c r="C3" s="77">
         <v>424</v>
       </c>
-      <c r="D3" s="52">
+      <c r="D3" s="73">
         <v>0.340168670250241</v>
       </c>
-      <c r="E3" s="53">
+      <c r="E3" s="74">
         <v>0.151641756532511</v>
       </c>
-      <c r="F3" s="54">
+      <c r="F3" s="75">
         <v>0.480950418849555</v>
       </c>
-      <c r="G3" s="55">
+      <c r="G3" s="76">
         <v>0.0272391543676918</v>
       </c>
     </row>
@@ -6987,19 +9781,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="56">
+      <c r="C4" s="77">
         <v>424</v>
       </c>
-      <c r="D4" s="52">
+      <c r="D4" s="73">
         <v>0.269323812514586</v>
       </c>
-      <c r="E4" s="53">
+      <c r="E4" s="74">
         <v>0.114968755379463</v>
       </c>
-      <c r="F4" s="54">
+      <c r="F4" s="75">
         <v>0.613035039499067</v>
       </c>
-      <c r="G4" s="55">
+      <c r="G4" s="76">
         <v>0.00267239260688501</v>
       </c>
     </row>
@@ -7014,19 +9808,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="56">
+      <c r="C5" s="77">
         <v>424</v>
       </c>
-      <c r="D5" s="52">
+      <c r="D5" s="73">
         <v>0.227066340396726</v>
       </c>
-      <c r="E5" s="53">
+      <c r="E5" s="74">
         <v>0.160502883572771</v>
       </c>
-      <c r="F5" s="54">
+      <c r="F5" s="75">
         <v>0.599145789699686</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="76">
         <v>0.0132849863308162</v>
       </c>
     </row>
@@ -7041,19 +9835,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="56">
+      <c r="C6" s="77">
         <v>416</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="73">
         <v>0.203585026025501</v>
       </c>
-      <c r="E6" s="53">
+      <c r="E6" s="74">
         <v>0.16629073661583</v>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="75">
         <v>0.614511780181818</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="76">
         <v>0.0156124571768507</v>
       </c>
     </row>
@@ -7068,19 +9862,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="77">
         <v>920</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="73">
         <v>0.185413051792005</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="74">
         <v>0.195631016550442</v>
       </c>
-      <c r="F7" s="54">
+      <c r="F7" s="75">
         <v>0.603456109570041</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="76">
         <v>0.0154998220875119</v>
       </c>
     </row>
@@ -7095,19 +9889,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="77">
         <v>352</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="73">
         <v>0.167205171581785</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="74">
         <v>0.113754184182276</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="75">
         <v>0.687612038931341</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="76">
         <v>0.0314286053045987</v>
       </c>
     </row>
@@ -7122,19 +9916,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="56">
+      <c r="C9" s="77">
         <v>365</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="73">
         <v>0.188903535865348</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="74">
         <v>0.116751739792445</v>
       </c>
-      <c r="F9" s="54">
+      <c r="F9" s="75">
         <v>0.686612593151121</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="76">
         <v>0.00773213119108642</v>
       </c>
     </row>
